--- a/artfynd/A 44132-2025 artfynd.xlsx
+++ b/artfynd/A 44132-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128048624</v>
+        <v>128048580</v>
       </c>
       <c r="B2" t="n">
-        <v>58042</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128048580</v>
+        <v>128048624</v>
       </c>
       <c r="B3" t="n">
-        <v>57954</v>
+        <v>58043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
         <v>128048575</v>
       </c>
       <c r="B4" t="n">
-        <v>58153</v>
+        <v>58154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44132-2025 artfynd.xlsx
+++ b/artfynd/A 44132-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128048580</v>
+        <v>128048624</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>58055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128048624</v>
+        <v>128048580</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>57967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
         <v>128048575</v>
       </c>
       <c r="B4" t="n">
-        <v>58154</v>
+        <v>58166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44132-2025 artfynd.xlsx
+++ b/artfynd/A 44132-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128048624</v>
+        <v>128048580</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>57967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128048580</v>
+        <v>128048624</v>
       </c>
       <c r="B3" t="n">
-        <v>57967</v>
+        <v>58055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 44132-2025 artfynd.xlsx
+++ b/artfynd/A 44132-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128048580</v>
+        <v>128048624</v>
       </c>
       <c r="B2" t="n">
-        <v>57967</v>
+        <v>58059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128048624</v>
+        <v>128048580</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>57971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +910,7 @@
         <v>128048575</v>
       </c>
       <c r="B4" t="n">
-        <v>58166</v>
+        <v>58170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
